--- a/Aps-BootUI/src/main/resources/excelTemplateModel/tm/胎面排程结果en.xlsx
+++ b/Aps-BootUI/src/main/resources/excelTemplateModel/tm/胎面排程结果en.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24729"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Gim\Svn\code\LL_APS\Aps-BootUI\src\main\resources\excelTemplateModel\tm\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\DC-APS\Aps-BootUI\src\main\resources\excelTemplateModel\tm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{611BE5CC-2996-43EE-8421-43B3F5CE1EF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD3B829A-C308-4F3C-B478-882E1B44C670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="胎面排程结果" sheetId="2" r:id="rId1"/>
@@ -25,12 +25,6 @@
     <t>基本信息</t>
   </si>
   <si>
-    <t>中班计划（12：00-0:00）</t>
-  </si>
-  <si>
-    <t>夜班计划（0:00-12:00）</t>
-  </si>
-  <si>
     <t>成型计划量</t>
   </si>
   <si>
@@ -70,50 +64,64 @@
     <t>库存供应成型时长(不生效)</t>
   </si>
   <si>
-    <t>中班计划量</t>
-  </si>
-  <si>
     <t>完成(不生效)</t>
   </si>
   <si>
-    <t>中班顺序</t>
-  </si>
-  <si>
     <t>完成率(不生效)</t>
   </si>
   <si>
-    <t>中班原因分析</t>
+    <t>一班(不生效)</t>
+  </si>
+  <si>
+    <t>二班(不生效)</t>
+  </si>
+  <si>
+    <t>三班(不生效)</t>
+  </si>
+  <si>
+    <t>次日一班(不生效)</t>
+  </si>
+  <si>
+    <t>次日二班(不生效)</t>
+  </si>
+  <si>
+    <t>胶料序号(不生效)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>补强/封口胶(不生效)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>夜班计划（19：00-7:00）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>夜班计划量</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>夜班顺序</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>夜班原因分析</t>
-  </si>
-  <si>
-    <t>一班(不生效)</t>
-  </si>
-  <si>
-    <t>二班(不生效)</t>
-  </si>
-  <si>
-    <t>三班(不生效)</t>
-  </si>
-  <si>
-    <t>次日一班(不生效)</t>
-  </si>
-  <si>
-    <t>次日二班(不生效)</t>
-  </si>
-  <si>
-    <t>胶料序号(不生效)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>补强/封口胶(不生效)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>早班计划量</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>早班顺序</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>早班原因分析</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>早班计划（7:00-19:00）</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -122,7 +130,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="178" formatCode="0_ "/>
+    <numFmt numFmtId="176" formatCode="0_ "/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -249,7 +257,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -259,37 +267,40 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -634,20 +645,20 @@
       <c r="M1" s="8"/>
       <c r="N1" s="8"/>
       <c r="O1" s="9" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="P1" s="10"/>
       <c r="Q1" s="10"/>
       <c r="R1" s="10"/>
       <c r="S1" s="10"/>
       <c r="T1" s="9" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="U1" s="10"/>
       <c r="V1" s="10"/>
       <c r="W1" s="11"/>
       <c r="X1" s="12" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y1" s="12"/>
       <c r="Z1" s="12"/>
@@ -656,88 +667,88 @@
     </row>
     <row r="2" spans="1:28" s="1" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="E2" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" s="13" t="s">
+      <c r="I2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="O2" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="P2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q2" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="T2" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="U2" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="W2" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="O2" s="6" t="s">
+      <c r="X2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="Y2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="Z2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="R2" s="5" t="s">
+      <c r="AA2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="S2" s="6" t="s">
+      <c r="AB2" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="U2" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="W2" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="X2" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="Y2" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="Z2" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA2" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB2" s="7" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
